--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/ba-uiux-medium.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/ba-uiux-medium.xlsx
@@ -460,19 +460,19 @@
         <v>Multi-step Form giúp giảm thiểu tải nhận thức (Cognitive Load). Người dùng thấy form ngắn ở từng bước sẽ ít nản lòng hơn so với một form dài dằng dặc.</v>
       </c>
       <c r="F2" t="str">
+        <v>Hiển thị toàn bộ 20 trường trên 1 trang duy nhất để người dùng không phải bấm nút chuyển trang — hiển thị tập trung</v>
+      </c>
+      <c r="G2" t="str">
         <v>Chia form thành các bước tuần tự (Multi-step Form) có thanh tiến trình hiển thị rõ ràng, kết hợp ẩn bớt các trường không bắt buộc — chia nhỏ quy trình</v>
       </c>
-      <c r="G2" t="str">
-        <v>Hiển thị toàn bộ 20 trường trên 1 trang duy nhất để người dùng không phải bấm nút chuyển trang — hiển thị tập trung</v>
-      </c>
       <c r="H2" t="str">
+        <v>Yêu cầu người dùng phải chụp ảnh căn cước công dân tải lên trước khi được phép nhập form — xác thực sớm</v>
+      </c>
+      <c r="I2" t="str">
         <v>Tự động báo lỗi đỏ ở tất cả các trường ngay khi người dùng vừa mới mở trang web lên — báo lỗi sớm</v>
       </c>
-      <c r="I2" t="str">
-        <v>Yêu cầu người dùng phải chụp ảnh căn cước công dân tải lên trước khi được phép nhập form — xác thực sớm</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Định luật Proximity chỉ ra rằng bộ não con người có xu hướng gom các vật thể đặt gần nhau thành một nhóm có chung đặc tính. Áp dụng vào UI, BA cần phân bổ khoảng cách (margin/padding) hợp lý để nhóm thông tin.</v>
       </c>
       <c r="F3" t="str">
+        <v>Thiết kế giao diện chỉ sử dụng duy nhất một font chữ cho tất cả các tiêu đề và nội dung — đồng bộ font</v>
+      </c>
+      <c r="G3" t="str">
         <v>Các phần tử có mối quan hệ nghiệp vụ mật thiết với nhau cần được đặt gần nhau về mặt không gian địa lý để người dùng tự hiểu chúng thuộc cùng một nhóm — nhóm các phần tử liên quan</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Đặt nút hủy giao dịch ngay sát nút xác nhận thanh toán để người dùng dễ chọn lựa nhanh chóng — đặt gần nút thao tác</v>
       </c>
       <c r="H3" t="str">
         <v>Tự động phóng to kích thước của hình ảnh sản phẩm lên gấp 5 lần khi di chuột qua — phóng to hình ảnh</v>
       </c>
       <c r="I3" t="str">
-        <v>Thiết kế giao diện chỉ sử dụng duy nhất một font chữ cho tất cả các tiêu đề và nội dung — đồng bộ font</v>
+        <v>Đặt nút hủy giao dịch ngay sát nút xác nhận thanh toán để người dùng dễ chọn lựa nhanh chóng — đặt gần nút thao tác</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -530,10 +530,10 @@
         <v>Mức giá tối đa mà khách hàng sẵn sàng trả tiền để mua bản quyền sử dụng phần mềm — khả năng chi trả tài chính</v>
       </c>
       <c r="H4" t="str">
+        <v>Tốc độ phản hồi trung bình của giao diện sau khi người dùng thực hiện một click chuột — tốc độ tương tác</v>
+      </c>
+      <c r="I4" t="str">
         <v>Tổng số lượng trang màn hình tối đa của một bản thiết kế Figma hoàn chỉnh — quy mô thiết kế</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Tốc độ phản hồi trung bình của giao diện sau khi người dùng thực hiện một click chuột — tốc độ tương tác</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -556,19 +556,19 @@
         <v>Thiết kế trạng thái lỗi tốt giúp giảm tỷ lệ bỏ rơi ứng dụng. Thông báo lỗi mơ hồ kiểu "Đã có lỗi xảy ra" mà không chỉ rõ cách sửa sẽ làm người dùng ức chế và rời bỏ hệ thống.</v>
       </c>
       <c r="F5" t="str">
-        <v>Để chỉ ra rõ ràng lỗi xảy ra ở đâu, nguyên nhân là gì và hướng dẫn cụ thể cách khắc phục (ví dụ: mật khẩu thiếu ký tự số) để người dùng hoàn thành tác vụ — giải quyết tắc nghẽn trải nghiệm</v>
+        <v>Để hiển thị quảng cáo của các bên đối tác trong thời gian hệ thống tải trang báo lỗi — hiển thị quảng cáo</v>
       </c>
       <c r="G5" t="str">
         <v>Để hệ thống tự động trừ tiền phạt trong tài khoản của khách hàng khi họ nhập sai thông tin — phạt người dùng</v>
       </c>
       <c r="H5" t="str">
+        <v>Để chỉ ra rõ ràng lỗi xảy ra ở đâu, nguyên nhân là gì và hướng dẫn cụ thể cách khắc phục (ví dụ: mật khẩu thiếu ký tự số) để người dùng hoàn thành tác vụ — giải quyết tắc nghẽn trải nghiệm</v>
+      </c>
+      <c r="I5" t="str">
         <v>Để lập trình viên có thể đổ lỗi cho người dùng khi hệ thống gặp lỗi logic code — đổ lỗi cho người dùng</v>
       </c>
-      <c r="I5" t="str">
-        <v>Để hiển thị quảng cáo của các bên đối tác trong thời gian hệ thống tải trang báo lỗi — hiển thị quảng cáo</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>Hệ thống lưới linh hoạt (Fluid Grid) là cốt lõi của Responsive Web Design, giúp giao diện tự thích ứng (adapt) mượt mà với mọi kích thước chiều rộng màn hình từ điện thoại, tablet đến desktop.</v>
       </c>
       <c r="F6" t="str">
-        <v>Grid cố định sử dụng đơn vị pixels (px) để định dạng chiều rộng; Grid linh hoạt sử dụng đơn vị phần trăm (%) để tự động co giãn theo kích thước màn hình — pixels vs phần trăm co giãn</v>
+        <v>Grid cố định tự động khóa màn hình của người dùng khi có cuộc gọi điện thoại đến — bảo mật cuộc gọi</v>
       </c>
       <c r="G6" t="str">
         <v>Grid cố định chỉ dùng cho thiết kế đen trắng; Grid linh hoạt bắt buộc phải có tối thiểu 12 màu sắc — phân biệt màu sắc lưới</v>
       </c>
       <c r="H6" t="str">
+        <v>Grid cố định sử dụng đơn vị pixels (px) để định dạng chiều rộng; Grid linh hoạt sử dụng đơn vị phần trăm (%) để tự động co giãn theo kích thước màn hình — pixels vs phần trăm co giãn</v>
+      </c>
+      <c r="I6" t="str">
         <v>Grid cố định do lập trình viên tự quyết định; Grid linh hoạt do BA vẽ bằng tay trên giấy — phân vai trò vẽ lưới</v>
       </c>
-      <c r="I6" t="str">
-        <v>Grid cố định tự động khóa màn hình của người dùng khi có cuộc gọi điện thoại đến — bảo mật cuộc gọi</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>IA quyết định sơ đồ trang web (Sitemap), cách dán nhãn các danh mục (Menu labels) và luồng điều hướng. IA tốt giúp người dùng định hình được cấu trúc trang web và không bị lạc.</v>
       </c>
       <c r="F7" t="str">
+        <v>Bảng thống kê số lượng bài viết đăng tải trên trang tin tức hàng tháng — quản lý nội dung</v>
+      </c>
+      <c r="G7" t="str">
         <v>Cách thức tổ chức, phân cấp cấu trúc thông tin và sơ đồ điều hướng của website giúp người dùng tìm kiếm thông tin dễ dàng nhất — sơ đồ cấu trúc thông tin</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Mô hình vật lý kết nối các máy chủ lưu trữ dữ liệu SQL của dự án — kiến trúc máy chủ</v>
       </c>
       <c r="H7" t="str">
         <v>Quy trình nén các tệp tin hình ảnh đồ họa để lưu trữ trên Cloud — quy trình nén ảnh</v>
       </c>
       <c r="I7" t="str">
-        <v>Bảng thống kê số lượng bài viết đăng tải trên trang tin tức hàng tháng — quản lý nội dung</v>
+        <v>Mô hình vật lý kết nối các máy chủ lưu trữ dữ liệu SQL của dự án — kiến trúc máy chủ</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -652,7 +652,7 @@
         <v>Inline Validation giúp người dùng sửa sai ngay lập tức tại thời điểm nhập, giảm thời gian và sự ức chế so với việc bấm Submit rồi mới thấy danh sách lỗi hiển thị.</v>
       </c>
       <c r="F8" t="str">
-        <v>Kiểm tra và báo lỗi dữ liệu ngay tại ô nhập liệu khi người dùng vừa rời khỏi ô đó, thay vì đợi bấm nút Submit mới báo lỗi — phản hồi thời gian thực</v>
+        <v>Bắt buộc người dùng phải nhập thông tin mật khẩu hai lần trước khi đăng ký — xác thực mật khẩu</v>
       </c>
       <c r="G8" t="str">
         <v>Tự động gửi email thông báo cho khách hàng mỗi khi họ nhập xong một ô thông tin — thông báo qua email</v>
@@ -661,10 +661,10 @@
         <v>Ẩn toàn bộ các ô nhập liệu khác và chỉ hiển thị ô đang bị lỗi trên màn hình — tập trung ô lỗi</v>
       </c>
       <c r="I8" t="str">
-        <v>Bắt buộc người dùng phải nhập thông tin mật khẩu hai lần trước khi đăng ký — xác thực mật khẩu</v>
+        <v>Kiểm tra và báo lỗi dữ liệu ngay tại ô nhập liệu khi người dùng vừa rời khỏi ô đó, thay vì đợi bấm nút Submit mới báo lỗi — phản hồi thời gian thực</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -690,10 +690,10 @@
         <v>Radio Button dùng để nghe nhạc; Checkbox dùng để xem video trên trang web — phân loại đa phương tiện</v>
       </c>
       <c r="H9" t="str">
+        <v>Radio Button chỉ dùng trên điện thoại; Checkbox chỉ sử dụng trên màn hình máy tính — phân loại thiết bị</v>
+      </c>
+      <c r="I9" t="str">
         <v>Radio Button bắt buộc phải hiển thị dạng hình vuông; Checkbox hiển thị dạng hình tròn — hình dạng phần tử</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Radio Button chỉ dùng trên điện thoại; Checkbox chỉ sử dụng trên màn hình máy tính — phân loại thiết bị</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -716,19 +716,19 @@
         <v>Skeleton Screen thay thế cho spinner quay tròn truyền thống. Bằng cách hiển thị trước khung xương bố cục, nó hướng sự chú ý của người dùng vào nội dung sắp tải, giúp giảm cảm giác chờ đợi mệt mỏi.</v>
       </c>
       <c r="F10" t="str">
+        <v>Biểu thị sơ đồ cấu trúc xương của nhân vật hoạt hình 3D trong game — đồ họa game 3D</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Đại diện cho chế độ ban đêm (Dark Mode) của ứng dụng di động — chế độ ban đêm</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Đánh dấu các khu vực giao diện đang bị khóa tính năng đối với tài khoản thường — khóa tính năng</v>
+      </c>
+      <c r="I10" t="str">
         <v>Biểu thị giao diện tải tạm thời (dạng các khối màu xám mô phỏng layout) để người dùng có cảm giác hệ thống tải nhanh hơn — tăng hiệu năng cảm nhận (Perceived Performance)</v>
       </c>
-      <c r="G10" t="str">
-        <v>Biểu thị sơ đồ cấu trúc xương của nhân vật hoạt hình 3D trong game — đồ họa game 3D</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Đại diện cho chế độ ban đêm (Dark Mode) của ứng dụng di động — chế độ ban đêm</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Đánh dấu các khu vực giao diện đang bị khóa tính năng đối với tài khoản thường — khóa tính năng</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Định luật Jakob khuyên chúng ta nên tôn trọng các mô thức thiết kế quen thuộc (Design Patterns). Ví dụ: Giỏ hàng đặt góc trên bên phải, Avatar bấm vào ra menu cá nhân. Sáng tạo quá mức phá vỡ thói quen sẽ tăng rào cản sử dụng của người dùng.</v>
       </c>
       <c r="F11" t="str">
+        <v>Mỗi năm doanh nghiệp phải đập đi xây lại giao diện trang web một lần để tạo sự mới mẻ — làm mới giao diện</v>
+      </c>
+      <c r="G11" t="str">
         <v>Người dùng dành phần lớn thời gian trên các hệ thống khác, vì vậy họ mong muốn hệ thống của bạn hoạt động giống các hệ thống họ đã quen thuộc — thói quen tương tác của người dùng</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Giao diện càng chứa nhiều màu sắc rực rỡ thì người dùng càng ở lại trang web lâu hơn — sử dụng màu sắc</v>
       </c>
       <c r="H11" t="str">
         <v>Hệ thống phải bắt buộc người dùng học một bộ phím tắt mới hoàn toàn để tăng năng suất — phím tắt tương tác</v>
       </c>
       <c r="I11" t="str">
-        <v>Mỗi năm doanh nghiệp phải đập đi xây lại giao diện trang web một lần để tạo sự mới mẻ — làm mới giao diện</v>
+        <v>Giao diện càng chứa nhiều màu sắc rực rỡ thì người dùng càng ở lại trang web lâu hơn — sử dụng màu sắc</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
